--- a/proba-growth/pricing/PROBA-PRICE-LIST.xlsx
+++ b/proba-growth/pricing/PROBA-PRICE-LIST.xlsx
@@ -9,9 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Прайс" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Прайс'!$A$1:$H$53</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -34,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -44,11 +42,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0018181B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
       </patternFill>
     </fill>
   </fills>
@@ -64,18 +57,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -527,7 +515,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -567,14 +555,14 @@
           <t>15–40 тыс.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>партнёр подтверждает</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -607,14 +595,14 @@
           <t>5–20 тыс.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>партнёр подтверждает</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -647,14 +635,14 @@
           <t>45–250 тыс., медиана 90–135</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>партнёр подтверждает</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -687,14 +675,14 @@
           <t>9–20 тыс.</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>партнёр подтверждает</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -727,14 +715,14 @@
           <t>9–25 тыс.</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>партнёр подтверждает</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -767,14 +755,14 @@
           <t>30–150 тыс.</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>партнёр подтверждает</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -807,14 +795,14 @@
           <t>9,5–35 тыс.</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>партнёр подтверждает</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -885,14 +873,14 @@
           <t>15–92 тыс.</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>партнёр подтверждает</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -925,14 +913,14 @@
           <t>25–80 тыс.</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>партнёр подтверждает</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1041,14 +1029,14 @@
           <t>10–30 тыс.</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>партнёр подтверждает</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1069,7 @@
           <t>фриланс ниже, агентства выше</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -1121,7 +1109,7 @@
           <t>1,5–10 тыс. фриланс / 50–200 тыс. агентства</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -1161,7 +1149,7 @@
           <t>40–380 тыс. агентства</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -1239,7 +1227,7 @@
           <t>25–80 тыс. агентства / 35–130 тыс. профильные</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -1317,7 +1305,7 @@
           <t>1–5 тыс. фриланс / 16–32 тыс. агентства</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -1357,7 +1345,7 @@
           <t>5–32 тыс. фриланс / 30–130 тыс. агентства / 100–200 тыс. Новосибирск</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -1435,7 +1423,7 @@
           <t>нет надёжных данных по Новосибирску</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -1475,7 +1463,7 @@
           <t>в пределах рынка</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -1515,7 +1503,7 @@
           <t>в пределах рынка</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -1593,7 +1581,7 @@
           <t>1–15 тыс. фриланс / 15–100 тыс. агентства</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -1633,7 +1621,7 @@
           <t>15–40 тыс. фриланс / 25–150 тыс. агентства</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -1673,7 +1661,7 @@
           <t>1–3 тыс. фриланс / 8–12 тыс. агентства</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -1713,7 +1701,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -1753,7 +1741,7 @@
           <t>21,6–50 тыс.</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -1905,7 +1893,7 @@
           <t>0,6–5 тыс. фриланс / 10–20 тыс. агентства</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -1945,7 +1933,7 @@
           <t>25–50 тыс.</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -1985,7 +1973,7 @@
           <t>мало данных (n ≤ 2)</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2025,7 +2013,7 @@
           <t>30–37 тыс. фриланс / 60–380 тыс. агентства</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2065,7 +2053,7 @@
           <t>7–16 тыс. фриланс / от 20 тыс. агентства</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2105,7 +2093,7 @@
           <t>мало данных</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2145,7 +2133,7 @@
           <t>мало данных</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2185,7 +2173,7 @@
           <t>0,5–1,1 тыс. за звонок / 3–10 тыс. отчёт</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2225,7 +2213,7 @@
           <t>3,9–52 тыс.</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2265,7 +2253,7 @@
           <t>от 30 тыс. агентства</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2305,7 +2293,7 @@
           <t>50–100 тыс., премиум 240 тыс.</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2345,7 +2333,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2385,7 +2373,7 @@
           <t>25–65 тыс., медиана 40</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2425,7 +2413,7 @@
           <t>5–19,5 тыс. фриланс / 100–200 тыс. студии</t>
         </is>
       </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2465,7 +2453,7 @@
           <t>19,5–104 тыс. (только фриланс)</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>да</t>
         </is>
@@ -2551,7 +2539,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/proba-growth/pricing/PROBA-PRICE-LIST.xlsx
+++ b/proba-growth/pricing/PROBA-PRICE-LIST.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2538,6 +2538,286 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Маркетинг</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>3D-визуализация упаковки, 1 SKU</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3D-модель упаковки по макету, 3–5 ракурсов, файлы для карточки, сайта и презентации. Можно до выпуска первой партии</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>за SKU</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>5–30 тыс. за продукт; 1,5–3 тыс. за ракурс у фрилансеров</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>рекомендация (рынок, 2026-10-27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Маркетинг</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>3D-визуализация линейки</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>От 5 SKU в едином стиле: общая сцена, свет, ракурсы</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>за SKU</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>скидка за серию 30–50 %</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>рекомендация (рынок, 2026-10-27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Маркетинг</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>3D key visual для баннера и лендинга</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Сложная сцена: окружение, текстуры, ингредиенты, композиция под баннер или первый экран</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>за сцену</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>40–80 тыс.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>рекомендация (рынок, 2026-10-27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Маркетинг</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Видео для карточки маркетплейса (3D/моушн)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ролик до 15 секунд из 3D-модели: вращение, раскрытие состава, ключевые аргументы</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>за ролик</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>простая анимация от 3 тыс.; 3D-ролик 15–30 с от 65 тыс.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>рекомендация (рынок, 2026-10-27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Маркетинг</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Рекламный 3D-ролик</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>15–30 секунд, сценарий, 3D и моушн-графика, версии под площадки</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>65000</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>за ролик</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>от 65 тыс. (15–30 с); CGI до 60 с от 150 тыс.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>рекомендация (рынок, 2026-10-27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Маркетинг</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Пакет «Упаковка до регистрации», 1 SKU</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Дизайн этикетки по требованиям + 3D-визуализация + видео для карточки: можно готовить продажи, пока идёт СГР</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>за SKU</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>по частям 85 тыс. у нас</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>рекомендация (рынок, 2026-10-27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Маркетинг</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Исследование клиентов: JTBD-интервью и CJM</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Интервью с покупателями, работы (jobs), барьеры, карта пути клиента от поиска до повторной покупки</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>разово</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>рынок не собран — проверить</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>рекомендация (рынок, 2026-10-27)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/proba-growth/pricing/PROBA-PRICE-LIST.xlsx
+++ b/proba-growth/pricing/PROBA-PRICE-LIST.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>утверждено на сайте</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>утверждено на сайте</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>утверждено на сайте; расшифровать «материал»</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>рекомендация (лицензии отдельно)</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>гипотеза — проверить спрос</t>
+          <t>утверждено владельцем (расчётная: рынок не собран), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>рекомендация (лицензия отдельно)</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>рекомендация</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>рекомендация (рынок, 2026-10-27)</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>рекомендация (рынок, 2026-10-27)</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>рекомендация (рынок, 2026-10-27)</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>рекомендация (рынок, 2026-10-27)</t>
+          <t>утверждено владельцем (расчётная: рынок не собран), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>рекомендация (рынок, 2026-10-27)</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>рекомендация (рынок, 2026-10-27)</t>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,207 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>рекомендация (рынок, 2026-10-27)</t>
+          <t>утверждено владельцем (расчётная: рынок не собран), 2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Маркетинг</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Инфографика карточки (6–7 слайдов)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Структура слайдов, дизайн, сверка заявлений с документами</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>за карточку</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>фриланс-комплект 1–13,6 тыс.; студии 8–10 тыс.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Маркетинг</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Дизайн упаковки, линейка 3–5 SKU</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Единая система упаковки линейки, макеты по требованиям к маркировке</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>за линейку</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>60–250 тыс. за линейку</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>утверждено владельцем (среднерыночная), 2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Документы</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Проверка карточек и заявлений для агентств</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Пакет 10 карточек: заявления (ст. 25 закона о рекламе), совпадение с документами, требования площадок; ответ за 48 часов</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>пакет 10 карточек</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>рынок не собран; от цены проверки этикетки</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>утверждено владельцем (расчётная: рынок не собран), 2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Документы</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Аудит ассортимента под правила площадок</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>До 50 SKU: документ, статус в реестре, наименование, маркировка; таблица рисков и план</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>до 50 SKU</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>рынок не собран; от аудита карточек и подготовки к проверке</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>утверждено владельцем (расчётная: рынок не собран), 2026-10-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Документы</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Мониторинг ассортимента (абонемент)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Проверка новых SKU и изменений правил площадок, напоминания о сроках документов</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>в месяц</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>рынок не собран; от сопровождения аналитики</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>утверждено владельцем (расчётная: рынок не собран), 2026-10-27</t>
         </is>
       </c>
     </row>
